--- a/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:58</t>
+          <t>2026-09-01 03:15:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:09:59</t>
+          <t>2026-09-01 03:15:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:01</t>
+          <t>2026-09-01 03:15:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:02</t>
+          <t>2026-09-01 03:15:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:02</t>
+          <t>2026-09-01 03:15:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:02</t>
+          <t>2026-09-01 03:15:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:02</t>
+          <t>2026-09-01 03:15:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:02</t>
+          <t>2026-09-01 03:15:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:53</t>
+          <t>2026-09-01 03:32:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:55</t>
+          <t>2026-09-01 03:32:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:56</t>
+          <t>2026-09-01 03:32:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:57</t>
+          <t>2026-09-01 03:32:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.51%588,000</t>
+          <t>13.58%588,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.51%</t>
+          <t>13.58%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.58%358</t>
+          <t>+0.28%359</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.03%1,215,000</t>
+          <t>4.18%1,215,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.5%101</t>
+          <t>0%101</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.66%3,832,000</t>
+          <t>3.72%3,832,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.37%136</t>
+          <t>0%136</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.64%2,828,000</t>
+          <t>3.69%2,828,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.62%53,000</t>
+          <t>3.61%53,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.78%138,000</t>
+          <t>2.70%138,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>584</v>
+        <v>4315</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.56%435,000</t>
+          <t>2.53%67,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>435000</v>
+        <v>67000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3925</v>
+        <v>3410</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.53%67,000</t>
+          <t>2.50%76,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>67000</v>
+        <v>76000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.45%47,000</t>
+          <t>2.48%47,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3425</v>
+        <v>610</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.42%76,000</t>
+          <t>2.44%435,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>76000</v>
+        <v>435000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.14%72.5</t>
+          <t>+1.38%73.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.39%3,473,000</t>
+          <t>2.42%3,473,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.3%2270</t>
+          <t>+3.3%2345</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2270</v>
+        <v>2345</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.36%108,000</t>
+          <t>2.35%108,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>3661世芯電子</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.71%545</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.71%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>545</v>
+        <v>4275</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.17%383,000</t>
+          <t>2.07%53,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>383000</v>
+        <v>53000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>+4.22%568</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>999</v>
+        <v>568</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.13%202,000</t>
+          <t>2.00%383,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>202000</v>
+        <v>383000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:35</t>
+          <t>2026-09-01 15:29:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3661世芯電子</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.25%4075</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4075</v>
+        <v>2315</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.05%53,000</t>
+          <t>1.98%95,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>53000</v>
+        <v>95000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>+2.05%49.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2170</v>
+        <v>49.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.04%95,000</t>
+          <t>1.96%4,181,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>95000</v>
+        <v>4181000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-9.71%1395</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1395</v>
+        <v>971</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.02%138,000</t>
+          <t>1.94%202,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>138000</v>
+        <v>202000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.83%48.8</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>48.8</v>
+        <v>1865</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.92%4,181,000</t>
+          <t>1.86%105,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>4181000</v>
+        <v>105000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-9.71%5860</t>
+          <t>-6.09%1310</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5860</v>
+        <v>1310</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.91%31,000</t>
+          <t>1.85%138,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>31000</v>
+        <v>138000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1840</v>
+        <v>5870</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.82%105,000</t>
+          <t>1.74%31,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>105000</v>
+        <v>31000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.49%20.25</t>
+          <t>+0.49%20.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20.25</v>
+        <v>20.35</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.70%8,783,000</t>
+          <t>1.71%8,783,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>1301台灣塑膠工業</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.86%233.5</t>
+          <t>+2.42%67.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>233.5</v>
+        <v>67.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.60%726,000</t>
+          <t>1.66%2,612,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>726000</v>
+        <v>2612000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1301台灣塑膠工業</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5.58%66.2</t>
+          <t>+1.93%238</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>66.2</v>
+        <v>238</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.55%2,612,000</t>
+          <t>1.63%726,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2612000</v>
+        <v>726000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-8.61%1380</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.61%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1380</v>
+        <v>5885</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.53%107,000</t>
+          <t>1.55%27,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>107000</v>
+        <v>27000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.19%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>8046南亞電路板</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5990</v>
+        <v>1225</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.48%27,000</t>
+          <t>1.48%125,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>27000</v>
+        <v>125000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8046南亞電路板</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1230</v>
+        <v>1375</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.47%125,000</t>
+          <t>1.42%110,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>125000</v>
+        <v>110000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>3491昇達科技</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.47%1345</t>
+          <t>+7.25%1480</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1345</v>
+        <v>1480</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.43%110,000</t>
+          <t>1.42%107,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>110000</v>
+        <v>107000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>3105穩懋半導體</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>+9.94%492</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1175</v>
+        <v>492</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.36%113,000</t>
+          <t>1.40%326,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>113000</v>
+        <v>326000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:36</t>
+          <t>2026-09-01 15:29:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3105穩懋半導體</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.94%447.5</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>447.5</v>
+        <v>1175</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.36%326,000</t>
+          <t>1.28%113,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>326000</v>
+        <v>113000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.66%76.2</t>
+          <t>0%76.2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.19%1,657,000</t>
+          <t>1.21%1,657,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1630</v>
+        <v>7580</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.13%74,000</t>
+          <t>1.18%16,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>74000</v>
+        <v>16000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>+0.31%1635</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7650</v>
+        <v>1635</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.07%16,000</t>
+          <t>1.16%74,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>16000</v>
+        <v>74000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.56%543</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>543</v>
+        <v>3425</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.99%193,000</t>
+          <t>1.05%31,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>193000</v>
+        <v>31000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3081聯亞光電工業</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-4.6%518</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3530</v>
+        <v>518</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.97%31,000</t>
+          <t>1.01%193,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>31000</v>
+        <v>193000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.2%677</t>
+          <t>+5.02%711</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+5.02%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.93%146,000</t>
+          <t>0.95%146,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6147頎邦科技</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.84%175.5</t>
+          <t>0%196</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>175.5</v>
+        <v>196</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.90%517,000</t>
+          <t>0.89%475,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>517000</v>
+        <v>475000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>+4.56%183.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.56%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>196</v>
+        <v>183.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.88%475,000</t>
+          <t>0.87%517,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>475000</v>
+        <v>517000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.55%182.5</t>
+          <t>-3.56%176</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>182.5</v>
+        <v>176</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.42%243,000</t>
+          <t>0.43%243,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-1.85%2125</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2165</v>
+        <v>2125</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.41%20,000</t>
+          <t>0.42%20,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.02%2410</t>
+          <t>+2.9%2480</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2410</v>
+        <v>2480</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2881富邦金融控股</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%144</t>
+          <t>+7%535</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>144</v>
+        <v>535</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.21%154,000</t>
+          <t>0.22%46,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>154000</v>
+        <v>46000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.77%129</t>
+          <t>+0.69%145</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.21%171,000</t>
+          <t>0.21%154,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>171000</v>
+        <v>154000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:37</t>
+          <t>2026-09-01 15:29:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+4.06%500</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>500</v>
+        <v>1225</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.21%46,000</t>
+          <t>0.21%19,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>46000</v>
+        <v>19000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:39</t>
+          <t>2026-09-01 15:29:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+3.1%1165</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1165</v>
+        <v>132.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.20%19,000</t>
+          <t>0.21%171,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>19000</v>
+        <v>171000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:39</t>
+          <t>2026-09-01 15:29:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.47%64.7</t>
+          <t>+2.78%66.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>64.7</v>
+        <v>66.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:39</t>
+          <t>2026-09-01 15:29:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1960</v>
+        <v>2030</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.10%5,000</t>
+          <t>0.09%5,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:39</t>
+          <t>2026-09-01 15:29:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-6.17%912</t>
+          <t>+8.99%994</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-6.17%</t>
+          <t>+8.99%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:39</t>
+          <t>2026-09-01 15:29:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-8.9%819</t>
+          <t>+6.72%874</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>+6.72%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>819</v>
+        <v>874</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:06</t>
+          <t>2026-09-01 17:54:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:07</t>
+          <t>2026-09-01 17:54:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:08</t>
+          <t>2026-09-01 17:54:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:10</t>
+          <t>2026-09-01 17:54:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:10</t>
+          <t>2026-09-01 17:54:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:10</t>
+          <t>2026-09-01 17:54:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:10</t>
+          <t>2026-09-01 17:54:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:10</t>
+          <t>2026-09-01 17:54:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:01</t>
+          <t>2026-09-01 19:36:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:03</t>
+          <t>2026-09-01 19:36:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:04</t>
+          <t>2026-09-01 19:36:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:05</t>
+          <t>2026-09-01 19:36:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:05</t>
+          <t>2026-09-01 19:36:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:05</t>
+          <t>2026-09-01 19:36:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:05</t>
+          <t>2026-09-01 19:36:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 17:54:05</t>
+          <t>2026-09-01 19:36:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
